--- a/Dataset/marmottes2025_renamedMB.xlsx
+++ b/Dataset/marmottes2025_renamedMB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\FDC_Savoie\Marmottes_Savoie_2025\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/SHARED/Git_Projects/Marmottes_Savoie_2025/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B6A4F1-B7C4-40E2-81EC-8CE5FB9996EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC953FD-0339-B346-B232-334BEA34A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25360" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025_Marmotte_Base_de_Donnees" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Parametrage_Both_Sites" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025_Marmotte_Base_de_Donnees'!$A$1:$O$553</definedName>
     <definedName name="Derangement">README!$O$2:$O$5</definedName>
     <definedName name="Dérangement">README!$G$2:$G$5</definedName>
     <definedName name="érangement">README!#REF!</definedName>
@@ -641,7 +642,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,7 +654,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -667,7 +668,6 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -875,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -911,7 +911,6 @@
     <xf numFmtId="45" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="45" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,9 +929,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -970,7 +969,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1076,7 +1075,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1218,7 +1217,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1227,26 +1226,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O553"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="56.81640625" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.453125" style="1"/>
+    <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="56.83203125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" customHeight="1">
+    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>195</v>
       </c>
@@ -1293,7 +1292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" customHeight="1">
+    <row r="2" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1337,7 +1336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="30" customHeight="1">
+    <row r="3" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1381,7 +1380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="30" customHeight="1">
+    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1425,7 +1424,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30" customHeight="1">
+    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1469,7 +1468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30" customHeight="1">
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -1513,7 +1512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30" customHeight="1">
+    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -1557,7 +1556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="30" customHeight="1">
+    <row r="8" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -1601,7 +1600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="30" customHeight="1">
+    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -1645,7 +1644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="30" customHeight="1">
+    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -1689,7 +1688,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="30" customHeight="1">
+    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="30" customHeight="1">
+    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -1777,7 +1776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="30" customHeight="1">
+    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="30" customHeight="1">
+    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="30" customHeight="1">
+    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="30" customHeight="1">
+    <row r="16" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="30" customHeight="1">
+    <row r="17" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -1997,7 +1996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="30" customHeight="1">
+    <row r="18" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
@@ -2038,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="30" customHeight="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
@@ -2085,7 +2084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30" customHeight="1">
+    <row r="20" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="30" customHeight="1">
+    <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="30" customHeight="1">
+    <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>2</v>
       </c>
@@ -2217,7 +2216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="30" customHeight="1">
+    <row r="23" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>2</v>
       </c>
@@ -2261,7 +2260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="30" customHeight="1">
+    <row r="24" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>2</v>
       </c>
@@ -2305,7 +2304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="30" customHeight="1">
+    <row r="25" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="30" customHeight="1">
+    <row r="26" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2393,7 +2392,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="30" customHeight="1">
+    <row r="27" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
@@ -2437,7 +2436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="30" customHeight="1">
+    <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
@@ -2481,7 +2480,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30" customHeight="1">
+    <row r="29" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="30" customHeight="1">
+    <row r="30" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="30" customHeight="1">
+    <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>21</v>
       </c>
@@ -2613,7 +2612,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1">
+    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>21</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="30" customHeight="1">
+    <row r="33" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="30" customHeight="1">
+    <row r="34" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>21</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="30" customHeight="1">
+    <row r="35" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>21</v>
       </c>
@@ -2789,7 +2788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="30" customHeight="1">
+    <row r="36" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>21</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="30" customHeight="1">
+    <row r="37" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>21</v>
       </c>
@@ -2877,7 +2876,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="30" customHeight="1">
+    <row r="38" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
@@ -2921,7 +2920,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="30" customHeight="1">
+    <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>21</v>
       </c>
@@ -2965,7 +2964,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="30" customHeight="1">
+    <row r="40" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>21</v>
       </c>
@@ -3009,7 +3008,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="30" customHeight="1">
+    <row r="41" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>21</v>
       </c>
@@ -3053,7 +3052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="30" customHeight="1">
+    <row r="42" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>21</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="30" customHeight="1">
+    <row r="43" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>21</v>
       </c>
@@ -3141,7 +3140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="30" customHeight="1">
+    <row r="44" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>21</v>
       </c>
@@ -3185,7 +3184,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="30" customHeight="1">
+    <row r="45" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -3229,7 +3228,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="30" customHeight="1">
+    <row r="46" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>21</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="30" customHeight="1">
+    <row r="47" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>21</v>
       </c>
@@ -3317,7 +3316,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1">
+    <row r="48" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
@@ -3361,7 +3360,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="30" customHeight="1">
+    <row r="49" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>21</v>
       </c>
@@ -3405,7 +3404,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="30" customHeight="1">
+    <row r="50" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>21</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="30" customHeight="1">
+    <row r="51" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>21</v>
       </c>
@@ -3493,7 +3492,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="30" customHeight="1">
+    <row r="52" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>21</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="30" customHeight="1">
+    <row r="53" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>21</v>
       </c>
@@ -3581,7 +3580,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="30" customHeight="1">
+    <row r="54" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>21</v>
       </c>
@@ -3625,7 +3624,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="30" customHeight="1">
+    <row r="55" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
@@ -3669,7 +3668,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="30" customHeight="1">
+    <row r="56" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
@@ -3713,7 +3712,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="30" customHeight="1">
+    <row r="57" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>21</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="30" customHeight="1">
+    <row r="58" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>2</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="30" customHeight="1">
+    <row r="59" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
@@ -3845,7 +3844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="30" customHeight="1">
+    <row r="60" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>2</v>
       </c>
@@ -3889,7 +3888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="30" customHeight="1">
+    <row r="61" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>2</v>
       </c>
@@ -3933,7 +3932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="30" customHeight="1">
+    <row r="62" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>2</v>
       </c>
@@ -3977,7 +3976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="30" customHeight="1">
+    <row r="63" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>2</v>
       </c>
@@ -4021,7 +4020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="30" customHeight="1">
+    <row r="64" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>2</v>
       </c>
@@ -4065,7 +4064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="30" customHeight="1">
+    <row r="65" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>2</v>
       </c>
@@ -4109,7 +4108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="30" customHeight="1">
+    <row r="66" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>2</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="30" customHeight="1">
+    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>2</v>
       </c>
@@ -4197,7 +4196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="30" customHeight="1">
+    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>2</v>
       </c>
@@ -4241,7 +4240,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="30" customHeight="1">
+    <row r="69" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>2</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="30" customHeight="1">
+    <row r="70" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>2</v>
       </c>
@@ -4329,7 +4328,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="30" customHeight="1">
+    <row r="71" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>2</v>
       </c>
@@ -4373,7 +4372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="30" customHeight="1">
+    <row r="72" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>2</v>
       </c>
@@ -4417,7 +4416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="30" customHeight="1">
+    <row r="73" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>2</v>
       </c>
@@ -4461,7 +4460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="30" customHeight="1">
+    <row r="74" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>2</v>
       </c>
@@ -4505,7 +4504,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="30" customHeight="1">
+    <row r="75" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>2</v>
       </c>
@@ -4549,7 +4548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="30" customHeight="1">
+    <row r="76" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>2</v>
       </c>
@@ -4593,7 +4592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="30" customHeight="1">
+    <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>2</v>
       </c>
@@ -4637,7 +4636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="30" customHeight="1">
+    <row r="78" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>2</v>
       </c>
@@ -4681,7 +4680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="30" customHeight="1">
+    <row r="79" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>2</v>
       </c>
@@ -4725,7 +4724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="30" customHeight="1">
+    <row r="80" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>2</v>
       </c>
@@ -4769,7 +4768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="30" customHeight="1">
+    <row r="81" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>2</v>
       </c>
@@ -4813,7 +4812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="30" customHeight="1">
+    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>2</v>
       </c>
@@ -4857,7 +4856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="30" customHeight="1">
+    <row r="83" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>2</v>
       </c>
@@ -4901,7 +4900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="30" customHeight="1">
+    <row r="84" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>2</v>
       </c>
@@ -4945,7 +4944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="30" customHeight="1">
+    <row r="85" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>2</v>
       </c>
@@ -4989,7 +4988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="30" customHeight="1">
+    <row r="86" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>2</v>
       </c>
@@ -5033,7 +5032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="30" customHeight="1">
+    <row r="87" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>2</v>
       </c>
@@ -5077,7 +5076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="30" customHeight="1">
+    <row r="88" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>2</v>
       </c>
@@ -5121,7 +5120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="30" customHeight="1">
+    <row r="89" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>2</v>
       </c>
@@ -5165,7 +5164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="30" customHeight="1">
+    <row r="90" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>2</v>
       </c>
@@ -5209,7 +5208,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="30" customHeight="1">
+    <row r="91" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>2</v>
       </c>
@@ -5253,7 +5252,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="30" customHeight="1">
+    <row r="92" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>2</v>
       </c>
@@ -5297,7 +5296,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="30" customHeight="1">
+    <row r="93" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>2</v>
       </c>
@@ -5341,7 +5340,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="30" customHeight="1">
+    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>2</v>
       </c>
@@ -5385,7 +5384,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="30" customHeight="1">
+    <row r="95" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>2</v>
       </c>
@@ -5429,7 +5428,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="30" customHeight="1">
+    <row r="96" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>2</v>
       </c>
@@ -5473,7 +5472,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="30" customHeight="1">
+    <row r="97" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>2</v>
       </c>
@@ -5517,7 +5516,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="30" customHeight="1">
+    <row r="98" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>21</v>
       </c>
@@ -5561,7 +5560,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="30" customHeight="1">
+    <row r="99" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>21</v>
       </c>
@@ -5605,7 +5604,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="30" customHeight="1">
+    <row r="100" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>21</v>
       </c>
@@ -5649,7 +5648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="30" customHeight="1">
+    <row r="101" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>21</v>
       </c>
@@ -5693,7 +5692,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="30" customHeight="1">
+    <row r="102" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>21</v>
       </c>
@@ -5737,7 +5736,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="30" customHeight="1">
+    <row r="103" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>21</v>
       </c>
@@ -5781,7 +5780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="30" customHeight="1">
+    <row r="104" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>21</v>
       </c>
@@ -5825,7 +5824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="30" customHeight="1">
+    <row r="105" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>21</v>
       </c>
@@ -5869,7 +5868,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="30" customHeight="1">
+    <row r="106" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>21</v>
       </c>
@@ -5913,7 +5912,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="30" customHeight="1">
+    <row r="107" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>21</v>
       </c>
@@ -5957,7 +5956,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="30" customHeight="1">
+    <row r="108" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>21</v>
       </c>
@@ -6001,7 +6000,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="30" customHeight="1">
+    <row r="109" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>21</v>
       </c>
@@ -6045,7 +6044,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="30" customHeight="1">
+    <row r="110" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>21</v>
       </c>
@@ -6089,7 +6088,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="30" customHeight="1">
+    <row r="111" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>21</v>
       </c>
@@ -6133,7 +6132,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="30" customHeight="1">
+    <row r="112" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>21</v>
       </c>
@@ -6177,7 +6176,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="30" customHeight="1">
+    <row r="113" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>21</v>
       </c>
@@ -6221,7 +6220,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="30" customHeight="1">
+    <row r="114" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>21</v>
       </c>
@@ -6265,7 +6264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="30" customHeight="1">
+    <row r="115" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>21</v>
       </c>
@@ -6309,7 +6308,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="30" customHeight="1">
+    <row r="116" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>21</v>
       </c>
@@ -6353,7 +6352,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="30" customHeight="1">
+    <row r="117" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>21</v>
       </c>
@@ -6397,7 +6396,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="30" customHeight="1">
+    <row r="118" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>21</v>
       </c>
@@ -6441,7 +6440,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="30" customHeight="1">
+    <row r="119" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>21</v>
       </c>
@@ -6485,7 +6484,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="30" customHeight="1">
+    <row r="120" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>21</v>
       </c>
@@ -6529,7 +6528,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="30" customHeight="1">
+    <row r="121" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>21</v>
       </c>
@@ -6573,7 +6572,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="30" customHeight="1">
+    <row r="122" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>2</v>
       </c>
@@ -6617,7 +6616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="30" customHeight="1">
+    <row r="123" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>2</v>
       </c>
@@ -6661,7 +6660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="30" customHeight="1">
+    <row r="124" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>2</v>
       </c>
@@ -6705,7 +6704,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="30" customHeight="1">
+    <row r="125" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>2</v>
       </c>
@@ -6749,7 +6748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="30" customHeight="1">
+    <row r="126" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>2</v>
       </c>
@@ -6793,7 +6792,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="30" customHeight="1">
+    <row r="127" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>2</v>
       </c>
@@ -6837,7 +6836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="30" customHeight="1">
+    <row r="128" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>2</v>
       </c>
@@ -6881,7 +6880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="30" customHeight="1">
+    <row r="129" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>2</v>
       </c>
@@ -6925,7 +6924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:14" ht="30" customHeight="1">
+    <row r="130" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>2</v>
       </c>
@@ -6969,7 +6968,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="30" customHeight="1">
+    <row r="131" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>2</v>
       </c>
@@ -7013,7 +7012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="30" customHeight="1">
+    <row r="132" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>2</v>
       </c>
@@ -7057,7 +7056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="30" customHeight="1">
+    <row r="133" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>2</v>
       </c>
@@ -7101,7 +7100,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="30" customHeight="1">
+    <row r="134" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>2</v>
       </c>
@@ -7145,7 +7144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:14" ht="30" customHeight="1">
+    <row r="135" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>2</v>
       </c>
@@ -7189,7 +7188,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="30" customHeight="1">
+    <row r="136" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>2</v>
       </c>
@@ -7233,7 +7232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="30" customHeight="1">
+    <row r="137" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>2</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="30" customHeight="1">
+    <row r="138" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>2</v>
       </c>
@@ -7321,7 +7320,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="30" customHeight="1">
+    <row r="139" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>2</v>
       </c>
@@ -7365,7 +7364,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="30" customHeight="1">
+    <row r="140" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>2</v>
       </c>
@@ -7409,7 +7408,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="30" customHeight="1">
+    <row r="141" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>2</v>
       </c>
@@ -7453,7 +7452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="30" customHeight="1">
+    <row r="142" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>2</v>
       </c>
@@ -7497,7 +7496,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="30" customHeight="1">
+    <row r="143" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>2</v>
       </c>
@@ -7541,7 +7540,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="30" customHeight="1">
+    <row r="144" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>2</v>
       </c>
@@ -7585,7 +7584,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:14" ht="30" customHeight="1">
+    <row r="145" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>2</v>
       </c>
@@ -7629,7 +7628,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="30" customHeight="1">
+    <row r="146" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>2</v>
       </c>
@@ -7673,7 +7672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="30" customHeight="1">
+    <row r="147" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>2</v>
       </c>
@@ -7717,7 +7716,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:14" ht="30" customHeight="1">
+    <row r="148" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>2</v>
       </c>
@@ -7761,7 +7760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="30" customHeight="1">
+    <row r="149" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>2</v>
       </c>
@@ -7805,7 +7804,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:14" ht="30" customHeight="1">
+    <row r="150" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>2</v>
       </c>
@@ -7849,7 +7848,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="30" customHeight="1">
+    <row r="151" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>2</v>
       </c>
@@ -7893,7 +7892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:14" ht="30" customHeight="1">
+    <row r="152" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>2</v>
       </c>
@@ -7937,7 +7936,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="30" customHeight="1">
+    <row r="153" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>2</v>
       </c>
@@ -7981,7 +7980,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="30" customHeight="1">
+    <row r="154" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>21</v>
       </c>
@@ -8025,7 +8024,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="30" customHeight="1">
+    <row r="155" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>21</v>
       </c>
@@ -8069,7 +8068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="30" customHeight="1">
+    <row r="156" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>21</v>
       </c>
@@ -8113,7 +8112,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="30" customHeight="1">
+    <row r="157" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>21</v>
       </c>
@@ -8157,7 +8156,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="30" customHeight="1">
+    <row r="158" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>21</v>
       </c>
@@ -8201,7 +8200,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="30" customHeight="1">
+    <row r="159" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>21</v>
       </c>
@@ -8245,7 +8244,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="30" customHeight="1">
+    <row r="160" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>21</v>
       </c>
@@ -8289,7 +8288,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="30" customHeight="1">
+    <row r="161" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>21</v>
       </c>
@@ -8333,7 +8332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="30" customHeight="1">
+    <row r="162" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>21</v>
       </c>
@@ -8377,7 +8376,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="30" customHeight="1">
+    <row r="163" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>21</v>
       </c>
@@ -8421,7 +8420,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="30" customHeight="1">
+    <row r="164" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>21</v>
       </c>
@@ -8465,7 +8464,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="30" customHeight="1">
+    <row r="165" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>21</v>
       </c>
@@ -8509,7 +8508,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="30" customHeight="1">
+    <row r="166" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>21</v>
       </c>
@@ -8553,7 +8552,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="30" customHeight="1">
+    <row r="167" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>21</v>
       </c>
@@ -8597,7 +8596,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="30" customHeight="1">
+    <row r="168" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>21</v>
       </c>
@@ -8641,7 +8640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="30" customHeight="1">
+    <row r="169" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>21</v>
       </c>
@@ -8685,7 +8684,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="30" customHeight="1">
+    <row r="170" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>21</v>
       </c>
@@ -8729,7 +8728,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="30" customHeight="1">
+    <row r="171" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>21</v>
       </c>
@@ -8773,7 +8772,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="30" customHeight="1">
+    <row r="172" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>21</v>
       </c>
@@ -8817,7 +8816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="173" spans="1:14" ht="30" customHeight="1">
+    <row r="173" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>21</v>
       </c>
@@ -8861,7 +8860,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="30" customHeight="1">
+    <row r="174" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>21</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="30" customHeight="1">
+    <row r="175" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>21</v>
       </c>
@@ -8949,7 +8948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="30" customHeight="1">
+    <row r="176" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>21</v>
       </c>
@@ -8993,7 +8992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:14" ht="30" customHeight="1">
+    <row r="177" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>21</v>
       </c>
@@ -9037,7 +9036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="178" spans="1:14" ht="30" customHeight="1">
+    <row r="178" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>21</v>
       </c>
@@ -9081,7 +9080,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="179" spans="1:14" ht="30" customHeight="1">
+    <row r="179" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>21</v>
       </c>
@@ -9125,7 +9124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="180" spans="1:14" ht="30" customHeight="1">
+    <row r="180" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>21</v>
       </c>
@@ -9169,7 +9168,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="30" customHeight="1">
+    <row r="181" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>21</v>
       </c>
@@ -9213,7 +9212,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:14" ht="30" customHeight="1">
+    <row r="182" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>2</v>
       </c>
@@ -9257,7 +9256,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="30" customHeight="1">
+    <row r="183" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>2</v>
       </c>
@@ -9301,7 +9300,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:14" ht="30" customHeight="1">
+    <row r="184" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>2</v>
       </c>
@@ -9345,7 +9344,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="185" spans="1:14" ht="30" customHeight="1">
+    <row r="185" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>2</v>
       </c>
@@ -9389,7 +9388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="186" spans="1:14" ht="30" customHeight="1">
+    <row r="186" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>2</v>
       </c>
@@ -9433,7 +9432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="187" spans="1:14" ht="30" customHeight="1">
+    <row r="187" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>2</v>
       </c>
@@ -9477,7 +9476,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="188" spans="1:14" ht="30" customHeight="1">
+    <row r="188" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>2</v>
       </c>
@@ -9521,7 +9520,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="30" customHeight="1">
+    <row r="189" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>2</v>
       </c>
@@ -9565,7 +9564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="190" spans="1:14" ht="30" customHeight="1">
+    <row r="190" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>2</v>
       </c>
@@ -9609,7 +9608,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="191" spans="1:14" ht="30" customHeight="1">
+    <row r="191" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>2</v>
       </c>
@@ -9653,7 +9652,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="192" spans="1:14" ht="30" customHeight="1">
+    <row r="192" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>2</v>
       </c>
@@ -9697,7 +9696,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="193" spans="1:15" ht="30" customHeight="1">
+    <row r="193" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>2</v>
       </c>
@@ -9741,7 +9740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="194" spans="1:15" ht="30" customHeight="1">
+    <row r="194" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>2</v>
       </c>
@@ -9785,7 +9784,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="195" spans="1:15" ht="30" customHeight="1">
+    <row r="195" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>2</v>
       </c>
@@ -9829,7 +9828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="196" spans="1:15" ht="30" customHeight="1">
+    <row r="196" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>2</v>
       </c>
@@ -9873,7 +9872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="197" spans="1:15" ht="30" customHeight="1">
+    <row r="197" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>2</v>
       </c>
@@ -9917,7 +9916,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="198" spans="1:15" ht="30" customHeight="1">
+    <row r="198" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>2</v>
       </c>
@@ -9961,7 +9960,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="30" customHeight="1">
+    <row r="199" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>2</v>
       </c>
@@ -10008,7 +10007,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="200" spans="1:15" ht="30" customHeight="1">
+    <row r="200" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>2</v>
       </c>
@@ -10055,7 +10054,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="201" spans="1:15" ht="30" customHeight="1">
+    <row r="201" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>2</v>
       </c>
@@ -10102,7 +10101,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="202" spans="1:15" ht="30" customHeight="1">
+    <row r="202" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>2</v>
       </c>
@@ -10149,7 +10148,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="203" spans="1:15" ht="30" customHeight="1">
+    <row r="203" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>2</v>
       </c>
@@ -10196,7 +10195,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="204" spans="1:15" ht="30" customHeight="1">
+    <row r="204" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>2</v>
       </c>
@@ -10243,7 +10242,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="205" spans="1:15" ht="30" customHeight="1">
+    <row r="205" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>2</v>
       </c>
@@ -10290,7 +10289,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="206" spans="1:15" ht="30" customHeight="1">
+    <row r="206" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>21</v>
       </c>
@@ -10334,7 +10333,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" spans="1:15" ht="30" customHeight="1">
+    <row r="207" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>21</v>
       </c>
@@ -10378,7 +10377,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" spans="1:15" ht="30" customHeight="1">
+    <row r="208" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>21</v>
       </c>
@@ -10422,7 +10421,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" spans="1:15" ht="30" customHeight="1">
+    <row r="209" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>21</v>
       </c>
@@ -10466,7 +10465,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="30" customHeight="1">
+    <row r="210" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>21</v>
       </c>
@@ -10510,7 +10509,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="30" customHeight="1">
+    <row r="211" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>21</v>
       </c>
@@ -10554,7 +10553,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="30" customHeight="1">
+    <row r="212" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>21</v>
       </c>
@@ -10598,7 +10597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="30" customHeight="1">
+    <row r="213" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>21</v>
       </c>
@@ -10642,7 +10641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="30" customHeight="1">
+    <row r="214" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>21</v>
       </c>
@@ -10689,7 +10688,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="30" customHeight="1">
+    <row r="215" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>21</v>
       </c>
@@ -10736,7 +10735,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="216" spans="1:15" ht="30" customHeight="1">
+    <row r="216" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>21</v>
       </c>
@@ -10783,7 +10782,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="30" customHeight="1">
+    <row r="217" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>21</v>
       </c>
@@ -10830,7 +10829,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="30" customHeight="1">
+    <row r="218" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>21</v>
       </c>
@@ -10877,7 +10876,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="30" customHeight="1">
+    <row r="219" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>21</v>
       </c>
@@ -10924,7 +10923,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="30" customHeight="1">
+    <row r="220" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>21</v>
       </c>
@@ -10971,7 +10970,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="30" customHeight="1">
+    <row r="221" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>21</v>
       </c>
@@ -11018,7 +11017,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="222" spans="1:15" ht="30" customHeight="1">
+    <row r="222" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>21</v>
       </c>
@@ -11062,7 +11061,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="30" customHeight="1">
+    <row r="223" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>21</v>
       </c>
@@ -11106,7 +11105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="30" customHeight="1">
+    <row r="224" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>21</v>
       </c>
@@ -11150,7 +11149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="225" spans="1:14" ht="30" customHeight="1">
+    <row r="225" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
         <v>21</v>
       </c>
@@ -11194,7 +11193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:14" ht="30" customHeight="1">
+    <row r="226" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>21</v>
       </c>
@@ -11238,7 +11237,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="227" spans="1:14" ht="30" customHeight="1">
+    <row r="227" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>21</v>
       </c>
@@ -11282,7 +11281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="228" spans="1:14" ht="30" customHeight="1">
+    <row r="228" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>21</v>
       </c>
@@ -11326,7 +11325,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="30" customHeight="1">
+    <row r="229" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>21</v>
       </c>
@@ -11370,7 +11369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="30" customHeight="1">
+    <row r="230" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>21</v>
       </c>
@@ -11414,7 +11413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="231" spans="1:14" ht="30" customHeight="1">
+    <row r="231" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
         <v>21</v>
       </c>
@@ -11458,7 +11457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="232" spans="1:14" ht="30" customHeight="1">
+    <row r="232" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>21</v>
       </c>
@@ -11502,7 +11501,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="233" spans="1:14" ht="30" customHeight="1">
+    <row r="233" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>21</v>
       </c>
@@ -11546,7 +11545,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="234" spans="1:14" ht="30" customHeight="1">
+    <row r="234" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>21</v>
       </c>
@@ -11590,7 +11589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="30" customHeight="1">
+    <row r="235" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>21</v>
       </c>
@@ -11634,7 +11633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="30" customHeight="1">
+    <row r="236" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
         <v>21</v>
       </c>
@@ -11678,7 +11677,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="30" customHeight="1">
+    <row r="237" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>21</v>
       </c>
@@ -11722,7 +11721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="30" customHeight="1">
+    <row r="238" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>21</v>
       </c>
@@ -11766,7 +11765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="30" customHeight="1">
+    <row r="239" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>21</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="30" customHeight="1">
+    <row r="240" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>21</v>
       </c>
@@ -11854,7 +11853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="30" customHeight="1">
+    <row r="241" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>21</v>
       </c>
@@ -11898,7 +11897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="242" spans="1:14" ht="30" customHeight="1">
+    <row r="242" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>21</v>
       </c>
@@ -11942,7 +11941,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="30" customHeight="1">
+    <row r="243" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>21</v>
       </c>
@@ -11986,7 +11985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="244" spans="1:14" ht="30" customHeight="1">
+    <row r="244" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>21</v>
       </c>
@@ -12030,7 +12029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="30" customHeight="1">
+    <row r="245" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>21</v>
       </c>
@@ -12074,7 +12073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="246" spans="1:14" ht="30" customHeight="1">
+    <row r="246" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>21</v>
       </c>
@@ -12118,7 +12117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="30" customHeight="1">
+    <row r="247" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>21</v>
       </c>
@@ -12162,7 +12161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="30" customHeight="1">
+    <row r="248" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>21</v>
       </c>
@@ -12206,7 +12205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="30" customHeight="1">
+    <row r="249" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>21</v>
       </c>
@@ -12250,7 +12249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="30" customHeight="1">
+    <row r="250" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>21</v>
       </c>
@@ -12294,7 +12293,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="30" customHeight="1">
+    <row r="251" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>21</v>
       </c>
@@ -12338,7 +12337,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="30" customHeight="1">
+    <row r="252" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>21</v>
       </c>
@@ -12382,7 +12381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="30" customHeight="1">
+    <row r="253" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>21</v>
       </c>
@@ -12426,7 +12425,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="30" customHeight="1">
+    <row r="254" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
         <v>21</v>
       </c>
@@ -12470,7 +12469,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="30" customHeight="1">
+    <row r="255" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
         <v>21</v>
       </c>
@@ -12514,7 +12513,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="256" spans="1:14" ht="30" customHeight="1">
+    <row r="256" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
         <v>21</v>
       </c>
@@ -12558,7 +12557,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="30" customHeight="1">
+    <row r="257" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
         <v>21</v>
       </c>
@@ -12602,7 +12601,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="258" spans="1:15" ht="30" customHeight="1">
+    <row r="258" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
         <v>21</v>
       </c>
@@ -12646,7 +12645,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="259" spans="1:15" ht="30" customHeight="1">
+    <row r="259" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
         <v>21</v>
       </c>
@@ -12690,7 +12689,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="260" spans="1:15" ht="30" customHeight="1">
+    <row r="260" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>21</v>
       </c>
@@ -12734,7 +12733,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="261" spans="1:15" ht="30" customHeight="1">
+    <row r="261" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
         <v>21</v>
       </c>
@@ -12778,7 +12777,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="30" customHeight="1">
+    <row r="262" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
         <v>21</v>
       </c>
@@ -12822,7 +12821,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="263" spans="1:15" ht="30" customHeight="1">
+    <row r="263" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>21</v>
       </c>
@@ -12866,7 +12865,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="264" spans="1:15" ht="30" customHeight="1">
+    <row r="264" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
         <v>21</v>
       </c>
@@ -12910,7 +12909,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="265" spans="1:15" ht="30" customHeight="1">
+    <row r="265" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
         <v>21</v>
       </c>
@@ -12954,7 +12953,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="266" spans="1:15" ht="30" customHeight="1">
+    <row r="266" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
         <v>21</v>
       </c>
@@ -12998,7 +12997,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="267" spans="1:15" ht="30" customHeight="1">
+    <row r="267" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
         <v>21</v>
       </c>
@@ -13042,7 +13041,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="268" spans="1:15" ht="30" customHeight="1">
+    <row r="268" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
         <v>21</v>
       </c>
@@ -13086,7 +13085,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="269" spans="1:15" ht="30" customHeight="1">
+    <row r="269" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
         <v>21</v>
       </c>
@@ -13130,7 +13129,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="270" spans="1:15" ht="30" customHeight="1">
+    <row r="270" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
         <v>21</v>
       </c>
@@ -13177,7 +13176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="271" spans="1:15" ht="30" customHeight="1">
+    <row r="271" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
         <v>21</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="272" spans="1:15" ht="30" customHeight="1">
+    <row r="272" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>21</v>
       </c>
@@ -13271,7 +13270,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="273" spans="1:15" ht="30" customHeight="1">
+    <row r="273" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
         <v>21</v>
       </c>
@@ -13318,7 +13317,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="274" spans="1:15" ht="30" customHeight="1">
+    <row r="274" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
         <v>21</v>
       </c>
@@ -13365,7 +13364,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="275" spans="1:15" ht="30" customHeight="1">
+    <row r="275" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
         <v>21</v>
       </c>
@@ -13412,7 +13411,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="276" spans="1:15" ht="30" customHeight="1">
+    <row r="276" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
         <v>21</v>
       </c>
@@ -13459,7 +13458,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="277" spans="1:15" ht="30" customHeight="1">
+    <row r="277" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
         <v>21</v>
       </c>
@@ -13506,7 +13505,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="278" spans="1:15" ht="30" customHeight="1">
+    <row r="278" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
         <v>21</v>
       </c>
@@ -13550,7 +13549,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="279" spans="1:15" ht="30" customHeight="1">
+    <row r="279" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
         <v>21</v>
       </c>
@@ -13594,7 +13593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="280" spans="1:15" ht="30" customHeight="1">
+    <row r="280" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>21</v>
       </c>
@@ -13638,7 +13637,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="281" spans="1:15" ht="30" customHeight="1">
+    <row r="281" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
         <v>21</v>
       </c>
@@ -13682,7 +13681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="282" spans="1:15" ht="30" customHeight="1">
+    <row r="282" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
         <v>21</v>
       </c>
@@ -13726,7 +13725,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="283" spans="1:15" ht="30" customHeight="1">
+    <row r="283" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
         <v>21</v>
       </c>
@@ -13770,7 +13769,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="284" spans="1:15" ht="30" customHeight="1">
+    <row r="284" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
         <v>21</v>
       </c>
@@ -13814,7 +13813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="285" spans="1:15" ht="30" customHeight="1">
+    <row r="285" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
         <v>21</v>
       </c>
@@ -13858,7 +13857,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="286" spans="1:15" ht="30" customHeight="1">
+    <row r="286" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
         <v>21</v>
       </c>
@@ -13902,7 +13901,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="287" spans="1:15" ht="30" customHeight="1">
+    <row r="287" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
         <v>21</v>
       </c>
@@ -13946,7 +13945,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="288" spans="1:15" ht="30" customHeight="1">
+    <row r="288" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
         <v>21</v>
       </c>
@@ -13990,7 +13989,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="289" spans="1:14" ht="30" customHeight="1">
+    <row r="289" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
         <v>21</v>
       </c>
@@ -14034,7 +14033,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="290" spans="1:14" ht="30" customHeight="1">
+    <row r="290" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
         <v>21</v>
       </c>
@@ -14078,7 +14077,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="291" spans="1:14" ht="30" customHeight="1">
+    <row r="291" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
         <v>21</v>
       </c>
@@ -14122,7 +14121,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="292" spans="1:14" ht="30" customHeight="1">
+    <row r="292" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
         <v>21</v>
       </c>
@@ -14166,7 +14165,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="293" spans="1:14" ht="30" customHeight="1">
+    <row r="293" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
         <v>21</v>
       </c>
@@ -14210,7 +14209,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="294" spans="1:14" ht="30" customHeight="1">
+    <row r="294" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
         <v>21</v>
       </c>
@@ -14254,7 +14253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="295" spans="1:14" ht="30" customHeight="1">
+    <row r="295" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>21</v>
       </c>
@@ -14298,7 +14297,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="296" spans="1:14" ht="30" customHeight="1">
+    <row r="296" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
         <v>21</v>
       </c>
@@ -14342,7 +14341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:14" ht="30" customHeight="1">
+    <row r="297" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
         <v>21</v>
       </c>
@@ -14386,7 +14385,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="298" spans="1:14" ht="30" customHeight="1">
+    <row r="298" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
         <v>21</v>
       </c>
@@ -14430,7 +14429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="299" spans="1:14" ht="30" customHeight="1">
+    <row r="299" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
         <v>21</v>
       </c>
@@ -14474,7 +14473,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="300" spans="1:14" ht="30" customHeight="1">
+    <row r="300" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
         <v>21</v>
       </c>
@@ -14518,7 +14517,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="301" spans="1:14" ht="30" customHeight="1">
+    <row r="301" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>21</v>
       </c>
@@ -14562,7 +14561,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="302" spans="1:14" ht="30" customHeight="1">
+    <row r="302" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
         <v>21</v>
       </c>
@@ -14606,7 +14605,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="303" spans="1:14" ht="30" customHeight="1">
+    <row r="303" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
         <v>21</v>
       </c>
@@ -14650,7 +14649,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="1:14" ht="30" customHeight="1">
+    <row r="304" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
         <v>21</v>
       </c>
@@ -14694,7 +14693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="305" spans="1:14" ht="30" customHeight="1">
+    <row r="305" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
         <v>21</v>
       </c>
@@ -14738,7 +14737,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="306" spans="1:14" ht="30" customHeight="1">
+    <row r="306" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
         <v>21</v>
       </c>
@@ -14782,7 +14781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="307" spans="1:14" ht="30" customHeight="1">
+    <row r="307" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
         <v>21</v>
       </c>
@@ -14826,7 +14825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="308" spans="1:14" ht="30" customHeight="1">
+    <row r="308" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
         <v>21</v>
       </c>
@@ -14870,7 +14869,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="309" spans="1:14" ht="30" customHeight="1">
+    <row r="309" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
         <v>21</v>
       </c>
@@ -14914,7 +14913,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="310" spans="1:14" ht="30" customHeight="1">
+    <row r="310" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
         <v>21</v>
       </c>
@@ -14958,7 +14957,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="311" spans="1:14" ht="30" customHeight="1">
+    <row r="311" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
         <v>21</v>
       </c>
@@ -15002,7 +15001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="312" spans="1:14" ht="30" customHeight="1">
+    <row r="312" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
         <v>21</v>
       </c>
@@ -15046,7 +15045,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="313" spans="1:14" ht="30" customHeight="1">
+    <row r="313" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
         <v>21</v>
       </c>
@@ -15090,7 +15089,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="314" spans="1:14" ht="30" customHeight="1">
+    <row r="314" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>2</v>
       </c>
@@ -15134,7 +15133,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="315" spans="1:14" ht="30" customHeight="1">
+    <row r="315" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
         <v>2</v>
       </c>
@@ -15178,7 +15177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="316" spans="1:14" ht="30" customHeight="1">
+    <row r="316" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
         <v>2</v>
       </c>
@@ -15222,7 +15221,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="317" spans="1:14" ht="30" customHeight="1">
+    <row r="317" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
         <v>2</v>
       </c>
@@ -15266,7 +15265,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="318" spans="1:14" ht="30" customHeight="1">
+    <row r="318" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
         <v>2</v>
       </c>
@@ -15310,7 +15309,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="319" spans="1:14" ht="30" customHeight="1">
+    <row r="319" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>2</v>
       </c>
@@ -15354,7 +15353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="320" spans="1:14" ht="30" customHeight="1">
+    <row r="320" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
         <v>2</v>
       </c>
@@ -15398,7 +15397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="321" spans="1:14" ht="30" customHeight="1">
+    <row r="321" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
         <v>2</v>
       </c>
@@ -15442,7 +15441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="322" spans="1:14" ht="30" customHeight="1">
+    <row r="322" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
         <v>2</v>
       </c>
@@ -15486,7 +15485,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="323" spans="1:14" ht="30" customHeight="1">
+    <row r="323" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
         <v>2</v>
       </c>
@@ -15530,7 +15529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="324" spans="1:14" ht="30" customHeight="1">
+    <row r="324" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
         <v>2</v>
       </c>
@@ -15574,7 +15573,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="325" spans="1:14" ht="30" customHeight="1">
+    <row r="325" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
         <v>2</v>
       </c>
@@ -15618,7 +15617,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="326" spans="1:14" ht="30" customHeight="1">
+    <row r="326" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
         <v>2</v>
       </c>
@@ -15662,7 +15661,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="327" spans="1:14" ht="30" customHeight="1">
+    <row r="327" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
         <v>2</v>
       </c>
@@ -15706,7 +15705,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="328" spans="1:14" ht="30" customHeight="1">
+    <row r="328" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
         <v>2</v>
       </c>
@@ -15750,7 +15749,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="329" spans="1:14" ht="30" customHeight="1">
+    <row r="329" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
         <v>2</v>
       </c>
@@ -15794,7 +15793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="330" spans="1:14" ht="30" customHeight="1">
+    <row r="330" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
         <v>2</v>
       </c>
@@ -15838,7 +15837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="331" spans="1:14" ht="30" customHeight="1">
+    <row r="331" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
         <v>2</v>
       </c>
@@ -15882,7 +15881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:14" ht="30" customHeight="1">
+    <row r="332" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>2</v>
       </c>
@@ -15926,7 +15925,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="333" spans="1:14" ht="30" customHeight="1">
+    <row r="333" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>2</v>
       </c>
@@ -15970,7 +15969,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="334" spans="1:14" ht="30" customHeight="1">
+    <row r="334" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
         <v>2</v>
       </c>
@@ -16014,7 +16013,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="335" spans="1:14" ht="30" customHeight="1">
+    <row r="335" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
         <v>2</v>
       </c>
@@ -16058,7 +16057,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="336" spans="1:14" ht="30" customHeight="1">
+    <row r="336" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
         <v>2</v>
       </c>
@@ -16102,7 +16101,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="337" spans="1:14" ht="30" customHeight="1">
+    <row r="337" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
         <v>2</v>
       </c>
@@ -16146,7 +16145,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="338" spans="1:14" ht="30" customHeight="1">
+    <row r="338" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
         <v>2</v>
       </c>
@@ -16190,7 +16189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="339" spans="1:14" ht="30" customHeight="1">
+    <row r="339" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
         <v>2</v>
       </c>
@@ -16234,7 +16233,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="340" spans="1:14" ht="30" customHeight="1">
+    <row r="340" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
         <v>2</v>
       </c>
@@ -16278,7 +16277,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="341" spans="1:14" ht="30" customHeight="1">
+    <row r="341" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
         <v>2</v>
       </c>
@@ -16322,7 +16321,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="342" spans="1:14" ht="30" customHeight="1">
+    <row r="342" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
         <v>2</v>
       </c>
@@ -16366,7 +16365,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="343" spans="1:14" ht="30" customHeight="1">
+    <row r="343" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
         <v>2</v>
       </c>
@@ -16410,7 +16409,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="344" spans="1:14" ht="30" customHeight="1">
+    <row r="344" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
         <v>2</v>
       </c>
@@ -16454,7 +16453,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="345" spans="1:14" ht="30" customHeight="1">
+    <row r="345" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
         <v>2</v>
       </c>
@@ -16498,7 +16497,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="346" spans="1:14" ht="30" customHeight="1">
+    <row r="346" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
         <v>2</v>
       </c>
@@ -16542,7 +16541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="347" spans="1:14" ht="30" customHeight="1">
+    <row r="347" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
         <v>2</v>
       </c>
@@ -16586,7 +16585,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="348" spans="1:14" ht="30" customHeight="1">
+    <row r="348" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
         <v>2</v>
       </c>
@@ -16630,7 +16629,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="349" spans="1:14" ht="30" customHeight="1">
+    <row r="349" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
         <v>2</v>
       </c>
@@ -16674,7 +16673,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="350" spans="1:14" ht="30" customHeight="1">
+    <row r="350" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
         <v>2</v>
       </c>
@@ -16718,7 +16717,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="351" spans="1:14" ht="30" customHeight="1">
+    <row r="351" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>2</v>
       </c>
@@ -16762,7 +16761,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="352" spans="1:14" ht="30" customHeight="1">
+    <row r="352" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
         <v>2</v>
       </c>
@@ -16806,7 +16805,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="353" spans="1:14" ht="30" customHeight="1">
+    <row r="353" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
         <v>2</v>
       </c>
@@ -16850,7 +16849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="354" spans="1:14" ht="30" customHeight="1">
+    <row r="354" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
         <v>2</v>
       </c>
@@ -16894,7 +16893,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="355" spans="1:14" ht="30" customHeight="1">
+    <row r="355" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
         <v>2</v>
       </c>
@@ -16938,7 +16937,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="356" spans="1:14" ht="30" customHeight="1">
+    <row r="356" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
         <v>2</v>
       </c>
@@ -16982,7 +16981,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="357" spans="1:14" ht="30" customHeight="1">
+    <row r="357" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
         <v>2</v>
       </c>
@@ -17026,7 +17025,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="358" spans="1:14" ht="30" customHeight="1">
+    <row r="358" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
         <v>2</v>
       </c>
@@ -17070,7 +17069,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="359" spans="1:14" ht="30" customHeight="1">
+    <row r="359" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
         <v>2</v>
       </c>
@@ -17114,7 +17113,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="360" spans="1:14" ht="30" customHeight="1">
+    <row r="360" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
         <v>2</v>
       </c>
@@ -17158,7 +17157,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="361" spans="1:14" ht="30" customHeight="1">
+    <row r="361" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
         <v>2</v>
       </c>
@@ -17202,7 +17201,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="362" spans="1:14" ht="30" customHeight="1">
+    <row r="362" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
         <v>2</v>
       </c>
@@ -17246,7 +17245,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="363" spans="1:14" ht="30" customHeight="1">
+    <row r="363" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
         <v>2</v>
       </c>
@@ -17290,7 +17289,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="364" spans="1:14" ht="30" customHeight="1">
+    <row r="364" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
         <v>2</v>
       </c>
@@ -17334,7 +17333,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="365" spans="1:14" ht="30" customHeight="1">
+    <row r="365" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
         <v>2</v>
       </c>
@@ -17378,7 +17377,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="366" spans="1:14" ht="30" customHeight="1">
+    <row r="366" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
         <v>2</v>
       </c>
@@ -17422,7 +17421,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="367" spans="1:14" ht="30" customHeight="1">
+    <row r="367" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
         <v>2</v>
       </c>
@@ -17466,7 +17465,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="368" spans="1:14" ht="30" customHeight="1">
+    <row r="368" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
         <v>2</v>
       </c>
@@ -17510,7 +17509,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="369" spans="1:14" ht="30" customHeight="1">
+    <row r="369" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
         <v>2</v>
       </c>
@@ -17554,7 +17553,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="370" spans="1:14" ht="30" customHeight="1">
+    <row r="370" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
         <v>2</v>
       </c>
@@ -17598,7 +17597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="371" spans="1:14" ht="30" customHeight="1">
+    <row r="371" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
         <v>2</v>
       </c>
@@ -17642,7 +17641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="372" spans="1:14" ht="30" customHeight="1">
+    <row r="372" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
         <v>2</v>
       </c>
@@ -17686,7 +17685,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="373" spans="1:14" ht="30" customHeight="1">
+    <row r="373" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
         <v>2</v>
       </c>
@@ -17730,7 +17729,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="374" spans="1:14" ht="30" customHeight="1">
+    <row r="374" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
         <v>2</v>
       </c>
@@ -17774,7 +17773,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="375" spans="1:14" ht="30" customHeight="1">
+    <row r="375" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
         <v>2</v>
       </c>
@@ -17818,7 +17817,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="376" spans="1:14" ht="30" customHeight="1">
+    <row r="376" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
         <v>2</v>
       </c>
@@ -17862,7 +17861,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="377" spans="1:14" ht="30" customHeight="1">
+    <row r="377" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
         <v>2</v>
       </c>
@@ -17906,7 +17905,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="378" spans="1:14" ht="30" customHeight="1">
+    <row r="378" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
         <v>2</v>
       </c>
@@ -17950,7 +17949,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="379" spans="1:14" ht="30" customHeight="1">
+    <row r="379" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
         <v>2</v>
       </c>
@@ -17994,7 +17993,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="380" spans="1:14" ht="30" customHeight="1">
+    <row r="380" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
         <v>2</v>
       </c>
@@ -18038,7 +18037,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="381" spans="1:14" ht="30" customHeight="1">
+    <row r="381" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>2</v>
       </c>
@@ -18082,7 +18081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="382" spans="1:14" ht="30" customHeight="1">
+    <row r="382" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
         <v>2</v>
       </c>
@@ -18126,7 +18125,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="383" spans="1:14" ht="30" customHeight="1">
+    <row r="383" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
         <v>2</v>
       </c>
@@ -18170,7 +18169,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="384" spans="1:14" ht="30" customHeight="1">
+    <row r="384" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
         <v>2</v>
       </c>
@@ -18214,7 +18213,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="385" spans="1:14" ht="30" customHeight="1">
+    <row r="385" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
         <v>2</v>
       </c>
@@ -18258,7 +18257,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="386" spans="1:14" ht="30" customHeight="1">
+    <row r="386" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>2</v>
       </c>
@@ -18302,7 +18301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="387" spans="1:14" ht="30" customHeight="1">
+    <row r="387" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>2</v>
       </c>
@@ -18346,7 +18345,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="388" spans="1:14" ht="30" customHeight="1">
+    <row r="388" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
         <v>2</v>
       </c>
@@ -18390,7 +18389,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="389" spans="1:14" ht="30" customHeight="1">
+    <row r="389" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
         <v>2</v>
       </c>
@@ -18434,7 +18433,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="390" spans="1:14" ht="30" customHeight="1">
+    <row r="390" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
         <v>2</v>
       </c>
@@ -18478,7 +18477,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="391" spans="1:14" ht="30" customHeight="1">
+    <row r="391" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>2</v>
       </c>
@@ -18522,7 +18521,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="392" spans="1:14" ht="30" customHeight="1">
+    <row r="392" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
         <v>2</v>
       </c>
@@ -18566,7 +18565,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="393" spans="1:14" ht="30" customHeight="1">
+    <row r="393" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
         <v>2</v>
       </c>
@@ -18610,7 +18609,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="394" spans="1:14" ht="30" customHeight="1">
+    <row r="394" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
         <v>2</v>
       </c>
@@ -18654,7 +18653,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="395" spans="1:14" ht="30" customHeight="1">
+    <row r="395" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>2</v>
       </c>
@@ -18698,7 +18697,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="396" spans="1:14" ht="30" customHeight="1">
+    <row r="396" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>2</v>
       </c>
@@ -18742,7 +18741,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="397" spans="1:14" ht="30" customHeight="1">
+    <row r="397" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
         <v>2</v>
       </c>
@@ -18786,7 +18785,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="398" spans="1:14" ht="30" customHeight="1">
+    <row r="398" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
         <v>2</v>
       </c>
@@ -18830,7 +18829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="399" spans="1:14" ht="30" customHeight="1">
+    <row r="399" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>2</v>
       </c>
@@ -18874,7 +18873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="400" spans="1:14" ht="30" customHeight="1">
+    <row r="400" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
         <v>2</v>
       </c>
@@ -18918,7 +18917,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="401" spans="1:14" ht="30" customHeight="1">
+    <row r="401" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
         <v>2</v>
       </c>
@@ -18962,7 +18961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="402" spans="1:14" ht="30" customHeight="1">
+    <row r="402" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
         <v>2</v>
       </c>
@@ -19006,7 +19005,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="403" spans="1:14" ht="30" customHeight="1">
+    <row r="403" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
         <v>2</v>
       </c>
@@ -19050,7 +19049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="404" spans="1:14" ht="30" customHeight="1">
+    <row r="404" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
         <v>2</v>
       </c>
@@ -19094,7 +19093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="405" spans="1:14" ht="30" customHeight="1">
+    <row r="405" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
         <v>2</v>
       </c>
@@ -19138,7 +19137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="406" spans="1:14" ht="30" customHeight="1">
+    <row r="406" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>21</v>
       </c>
@@ -19182,7 +19181,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="407" spans="1:14" ht="30" customHeight="1">
+    <row r="407" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
         <v>21</v>
       </c>
@@ -19226,7 +19225,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="408" spans="1:14" ht="30" customHeight="1">
+    <row r="408" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
         <v>21</v>
       </c>
@@ -19270,7 +19269,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="409" spans="1:14" ht="30" customHeight="1">
+    <row r="409" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
         <v>21</v>
       </c>
@@ -19314,7 +19313,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="410" spans="1:14" ht="30" customHeight="1">
+    <row r="410" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
         <v>21</v>
       </c>
@@ -19358,7 +19357,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="411" spans="1:14" ht="30" customHeight="1">
+    <row r="411" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
         <v>21</v>
       </c>
@@ -19402,7 +19401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="412" spans="1:14" ht="30" customHeight="1">
+    <row r="412" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
         <v>21</v>
       </c>
@@ -19446,7 +19445,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="413" spans="1:14" ht="30" customHeight="1">
+    <row r="413" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
         <v>21</v>
       </c>
@@ -19490,7 +19489,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="414" spans="1:14" ht="30" customHeight="1">
+    <row r="414" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>21</v>
       </c>
@@ -19534,7 +19533,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="415" spans="1:14" ht="30" customHeight="1">
+    <row r="415" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
         <v>21</v>
       </c>
@@ -19578,7 +19577,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="416" spans="1:14" ht="30" customHeight="1">
+    <row r="416" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
         <v>21</v>
       </c>
@@ -19622,7 +19621,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="417" spans="1:14" ht="30" customHeight="1">
+    <row r="417" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
         <v>21</v>
       </c>
@@ -19666,7 +19665,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="418" spans="1:14" ht="30" customHeight="1">
+    <row r="418" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
         <v>21</v>
       </c>
@@ -19710,7 +19709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="419" spans="1:14" ht="30" customHeight="1">
+    <row r="419" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
         <v>21</v>
       </c>
@@ -19754,7 +19753,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="420" spans="1:14" ht="30" customHeight="1">
+    <row r="420" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
         <v>21</v>
       </c>
@@ -19798,7 +19797,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="421" spans="1:14" ht="30" customHeight="1">
+    <row r="421" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
         <v>21</v>
       </c>
@@ -19842,7 +19841,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="422" spans="1:14" ht="30" customHeight="1">
+    <row r="422" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
         <v>21</v>
       </c>
@@ -19886,7 +19885,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="423" spans="1:14" ht="30" customHeight="1">
+    <row r="423" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
         <v>21</v>
       </c>
@@ -19930,7 +19929,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="424" spans="1:14" ht="30" customHeight="1">
+    <row r="424" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
         <v>21</v>
       </c>
@@ -19974,7 +19973,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="425" spans="1:14" ht="30" customHeight="1">
+    <row r="425" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
         <v>21</v>
       </c>
@@ -20018,7 +20017,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="426" spans="1:14" ht="30" customHeight="1">
+    <row r="426" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
         <v>21</v>
       </c>
@@ -20062,7 +20061,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="427" spans="1:14" ht="30" customHeight="1">
+    <row r="427" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
         <v>21</v>
       </c>
@@ -20106,7 +20105,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="428" spans="1:14" ht="30" customHeight="1">
+    <row r="428" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
         <v>21</v>
       </c>
@@ -20150,7 +20149,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="429" spans="1:14" ht="30" customHeight="1">
+    <row r="429" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
         <v>21</v>
       </c>
@@ -20194,7 +20193,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="430" spans="1:14" ht="30" customHeight="1">
+    <row r="430" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
         <v>21</v>
       </c>
@@ -20238,7 +20237,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="431" spans="1:14" ht="30" customHeight="1">
+    <row r="431" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
         <v>21</v>
       </c>
@@ -20282,7 +20281,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="432" spans="1:14" ht="30" customHeight="1">
+    <row r="432" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
         <v>21</v>
       </c>
@@ -20326,7 +20325,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="433" spans="1:15" ht="30" customHeight="1">
+    <row r="433" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
         <v>21</v>
       </c>
@@ -20370,7 +20369,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="434" spans="1:15" ht="30" customHeight="1">
+    <row r="434" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>21</v>
       </c>
@@ -20414,7 +20413,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="435" spans="1:15" ht="30" customHeight="1">
+    <row r="435" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
         <v>21</v>
       </c>
@@ -20458,7 +20457,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="436" spans="1:15" ht="30" customHeight="1">
+    <row r="436" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
         <v>21</v>
       </c>
@@ -20502,7 +20501,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="437" spans="1:15" ht="30" customHeight="1">
+    <row r="437" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
         <v>21</v>
       </c>
@@ -20546,7 +20545,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="438" spans="1:15" ht="30" customHeight="1">
+    <row r="438" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
         <v>21</v>
       </c>
@@ -20593,7 +20592,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="439" spans="1:15" ht="30" customHeight="1">
+    <row r="439" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
         <v>21</v>
       </c>
@@ -20640,7 +20639,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="440" spans="1:15" ht="30" customHeight="1">
+    <row r="440" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
         <v>21</v>
       </c>
@@ -20687,7 +20686,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="441" spans="1:15" ht="30" customHeight="1">
+    <row r="441" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
         <v>21</v>
       </c>
@@ -20734,7 +20733,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="442" spans="1:15" ht="30" customHeight="1">
+    <row r="442" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
         <v>21</v>
       </c>
@@ -20781,7 +20780,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="443" spans="1:15" ht="30" customHeight="1">
+    <row r="443" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
         <v>21</v>
       </c>
@@ -20828,7 +20827,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="444" spans="1:15" ht="30" customHeight="1">
+    <row r="444" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
         <v>21</v>
       </c>
@@ -20875,7 +20874,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="445" spans="1:15" ht="30" customHeight="1">
+    <row r="445" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
         <v>21</v>
       </c>
@@ -20922,7 +20921,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="446" spans="1:15" ht="30" customHeight="1">
+    <row r="446" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
         <v>21</v>
       </c>
@@ -20966,7 +20965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:15" ht="30" customHeight="1">
+    <row r="447" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
         <v>21</v>
       </c>
@@ -21010,7 +21009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="448" spans="1:15" ht="30" customHeight="1">
+    <row r="448" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
         <v>21</v>
       </c>
@@ -21054,7 +21053,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="449" spans="1:14" ht="30" customHeight="1">
+    <row r="449" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
         <v>21</v>
       </c>
@@ -21098,7 +21097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450" spans="1:14" ht="30" customHeight="1">
+    <row r="450" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
         <v>21</v>
       </c>
@@ -21142,7 +21141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451" spans="1:14" ht="30" customHeight="1">
+    <row r="451" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
         <v>21</v>
       </c>
@@ -21186,7 +21185,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="452" spans="1:14" ht="30" customHeight="1">
+    <row r="452" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
         <v>21</v>
       </c>
@@ -21230,7 +21229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453" spans="1:14" ht="30" customHeight="1">
+    <row r="453" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
         <v>21</v>
       </c>
@@ -21274,7 +21273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="454" spans="1:14" ht="30" customHeight="1">
+    <row r="454" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
         <v>2</v>
       </c>
@@ -21318,7 +21317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="455" spans="1:14" ht="30" customHeight="1">
+    <row r="455" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>2</v>
       </c>
@@ -21362,7 +21361,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="456" spans="1:14" ht="30" customHeight="1">
+    <row r="456" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
         <v>2</v>
       </c>
@@ -21406,7 +21405,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="457" spans="1:14" ht="30" customHeight="1">
+    <row r="457" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
         <v>2</v>
       </c>
@@ -21450,7 +21449,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="458" spans="1:14" ht="30" customHeight="1">
+    <row r="458" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
         <v>2</v>
       </c>
@@ -21494,7 +21493,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="459" spans="1:14" ht="30" customHeight="1">
+    <row r="459" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
         <v>2</v>
       </c>
@@ -21538,7 +21537,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="460" spans="1:14" ht="30" customHeight="1">
+    <row r="460" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
         <v>2</v>
       </c>
@@ -21582,7 +21581,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="461" spans="1:14" ht="30" customHeight="1">
+    <row r="461" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
         <v>2</v>
       </c>
@@ -21626,7 +21625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="462" spans="1:14" ht="30" customHeight="1">
+    <row r="462" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
         <v>2</v>
       </c>
@@ -21670,7 +21669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="463" spans="1:14" ht="30" customHeight="1">
+    <row r="463" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
         <v>2</v>
       </c>
@@ -21714,7 +21713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="464" spans="1:14" ht="30" customHeight="1">
+    <row r="464" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
         <v>2</v>
       </c>
@@ -21758,7 +21757,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="465" spans="1:14" ht="30" customHeight="1">
+    <row r="465" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
         <v>2</v>
       </c>
@@ -21802,7 +21801,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="466" spans="1:14" ht="30" customHeight="1">
+    <row r="466" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
         <v>2</v>
       </c>
@@ -21846,7 +21845,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="467" spans="1:14" ht="30" customHeight="1">
+    <row r="467" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
         <v>2</v>
       </c>
@@ -21890,7 +21889,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="468" spans="1:14" ht="30" customHeight="1">
+    <row r="468" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
         <v>2</v>
       </c>
@@ -21934,7 +21933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="469" spans="1:14" ht="30" customHeight="1">
+    <row r="469" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
         <v>2</v>
       </c>
@@ -21978,7 +21977,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="470" spans="1:14" ht="30" customHeight="1">
+    <row r="470" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
         <v>2</v>
       </c>
@@ -22022,7 +22021,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="471" spans="1:14" ht="30" customHeight="1">
+    <row r="471" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
         <v>2</v>
       </c>
@@ -22066,7 +22065,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="472" spans="1:14" ht="30" customHeight="1">
+    <row r="472" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
         <v>2</v>
       </c>
@@ -22110,7 +22109,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="473" spans="1:14" ht="30" customHeight="1">
+    <row r="473" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
         <v>2</v>
       </c>
@@ -22154,7 +22153,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="474" spans="1:14" ht="30" customHeight="1">
+    <row r="474" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
         <v>2</v>
       </c>
@@ -22198,7 +22197,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="475" spans="1:14" ht="30" customHeight="1">
+    <row r="475" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
         <v>2</v>
       </c>
@@ -22242,7 +22241,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="476" spans="1:14" ht="30" customHeight="1">
+    <row r="476" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
         <v>2</v>
       </c>
@@ -22286,7 +22285,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="477" spans="1:14" ht="30" customHeight="1">
+    <row r="477" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
         <v>2</v>
       </c>
@@ -22330,7 +22329,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="478" spans="1:14" ht="30" customHeight="1">
+    <row r="478" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
         <v>2</v>
       </c>
@@ -22374,7 +22373,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="479" spans="1:14" ht="30" customHeight="1">
+    <row r="479" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
         <v>2</v>
       </c>
@@ -22418,7 +22417,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="480" spans="1:14" ht="30" customHeight="1">
+    <row r="480" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
         <v>2</v>
       </c>
@@ -22462,7 +22461,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="481" spans="1:14" ht="30" customHeight="1">
+    <row r="481" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
         <v>2</v>
       </c>
@@ -22506,7 +22505,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="482" spans="1:14" ht="30" customHeight="1">
+    <row r="482" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
         <v>2</v>
       </c>
@@ -22550,7 +22549,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="483" spans="1:14" ht="30" customHeight="1">
+    <row r="483" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
         <v>2</v>
       </c>
@@ -22594,7 +22593,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="484" spans="1:14" ht="30" customHeight="1">
+    <row r="484" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
         <v>2</v>
       </c>
@@ -22638,7 +22637,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="485" spans="1:14" ht="30" customHeight="1">
+    <row r="485" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
         <v>2</v>
       </c>
@@ -22682,7 +22681,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="486" spans="1:14" ht="30" customHeight="1">
+    <row r="486" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
         <v>2</v>
       </c>
@@ -22726,7 +22725,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="487" spans="1:14" ht="30" customHeight="1">
+    <row r="487" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
         <v>2</v>
       </c>
@@ -22770,7 +22769,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="488" spans="1:14" ht="30" customHeight="1">
+    <row r="488" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
         <v>2</v>
       </c>
@@ -22814,7 +22813,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="489" spans="1:14" ht="30" customHeight="1">
+    <row r="489" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
         <v>2</v>
       </c>
@@ -22858,7 +22857,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="490" spans="1:14" ht="30" customHeight="1">
+    <row r="490" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
         <v>2</v>
       </c>
@@ -22902,7 +22901,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="491" spans="1:14" ht="30" customHeight="1">
+    <row r="491" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
         <v>2</v>
       </c>
@@ -22946,7 +22945,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="492" spans="1:14" ht="30" customHeight="1">
+    <row r="492" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
         <v>2</v>
       </c>
@@ -22990,7 +22989,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="493" spans="1:14" ht="30" customHeight="1">
+    <row r="493" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
         <v>2</v>
       </c>
@@ -23034,7 +23033,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="494" spans="1:14" ht="30" customHeight="1">
+    <row r="494" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
         <v>2</v>
       </c>
@@ -23078,7 +23077,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="495" spans="1:14" ht="30" customHeight="1">
+    <row r="495" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
         <v>2</v>
       </c>
@@ -23122,7 +23121,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="496" spans="1:14" ht="30" customHeight="1">
+    <row r="496" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
         <v>2</v>
       </c>
@@ -23166,7 +23165,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="497" spans="1:14" ht="30" customHeight="1">
+    <row r="497" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
         <v>2</v>
       </c>
@@ -23210,7 +23209,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="498" spans="1:14" ht="30" customHeight="1">
+    <row r="498" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
         <v>2</v>
       </c>
@@ -23254,7 +23253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="499" spans="1:14" ht="30" customHeight="1">
+    <row r="499" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
         <v>2</v>
       </c>
@@ -23298,7 +23297,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="500" spans="1:14" ht="30" customHeight="1">
+    <row r="500" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
         <v>2</v>
       </c>
@@ -23342,7 +23341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="501" spans="1:14" ht="30" customHeight="1">
+    <row r="501" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
         <v>2</v>
       </c>
@@ -23386,7 +23385,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="502" spans="1:14" ht="30" customHeight="1">
+    <row r="502" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
         <v>2</v>
       </c>
@@ -23430,7 +23429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="503" spans="1:14" ht="30" customHeight="1">
+    <row r="503" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
         <v>2</v>
       </c>
@@ -23474,7 +23473,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="504" spans="1:14" ht="30" customHeight="1">
+    <row r="504" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
         <v>2</v>
       </c>
@@ -23518,7 +23517,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="505" spans="1:14" ht="30" customHeight="1">
+    <row r="505" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
         <v>2</v>
       </c>
@@ -23562,7 +23561,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="506" spans="1:14" ht="30" customHeight="1">
+    <row r="506" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
         <v>2</v>
       </c>
@@ -23606,7 +23605,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="507" spans="1:14" ht="30" customHeight="1">
+    <row r="507" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
         <v>2</v>
       </c>
@@ -23650,7 +23649,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="508" spans="1:14" ht="30" customHeight="1">
+    <row r="508" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
         <v>2</v>
       </c>
@@ -23694,7 +23693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="509" spans="1:14" ht="30" customHeight="1">
+    <row r="509" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
         <v>2</v>
       </c>
@@ -23738,7 +23737,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="510" spans="1:14" ht="30" customHeight="1">
+    <row r="510" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
         <v>2</v>
       </c>
@@ -23782,7 +23781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="511" spans="1:14" ht="30" customHeight="1">
+    <row r="511" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
         <v>2</v>
       </c>
@@ -23826,7 +23825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="512" spans="1:14" ht="30" customHeight="1">
+    <row r="512" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
         <v>2</v>
       </c>
@@ -23870,7 +23869,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="513" spans="1:14" ht="30" customHeight="1">
+    <row r="513" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
         <v>2</v>
       </c>
@@ -23914,7 +23913,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="514" spans="1:14" ht="30" customHeight="1">
+    <row r="514" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
         <v>21</v>
       </c>
@@ -23958,7 +23957,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="515" spans="1:14" ht="30" customHeight="1">
+    <row r="515" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
         <v>21</v>
       </c>
@@ -24002,7 +24001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="516" spans="1:14" ht="30" customHeight="1">
+    <row r="516" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
         <v>21</v>
       </c>
@@ -24046,7 +24045,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="517" spans="1:14" ht="30" customHeight="1">
+    <row r="517" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
         <v>21</v>
       </c>
@@ -24090,7 +24089,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="518" spans="1:14" ht="30" customHeight="1">
+    <row r="518" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
         <v>21</v>
       </c>
@@ -24134,7 +24133,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="519" spans="1:14" ht="30" customHeight="1">
+    <row r="519" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
         <v>21</v>
       </c>
@@ -24178,7 +24177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="520" spans="1:14" ht="30" customHeight="1">
+    <row r="520" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
         <v>21</v>
       </c>
@@ -24222,7 +24221,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="521" spans="1:14" ht="30" customHeight="1">
+    <row r="521" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
         <v>21</v>
       </c>
@@ -24266,7 +24265,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="522" spans="1:14" ht="30" customHeight="1">
+    <row r="522" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="s">
         <v>21</v>
       </c>
@@ -24310,7 +24309,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="523" spans="1:14" ht="30" customHeight="1">
+    <row r="523" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
         <v>21</v>
       </c>
@@ -24354,7 +24353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="524" spans="1:14" ht="30" customHeight="1">
+    <row r="524" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="s">
         <v>21</v>
       </c>
@@ -24398,7 +24397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="525" spans="1:14" ht="30" customHeight="1">
+    <row r="525" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="s">
         <v>21</v>
       </c>
@@ -24442,7 +24441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="526" spans="1:14" ht="30" customHeight="1">
+    <row r="526" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="s">
         <v>21</v>
       </c>
@@ -24486,7 +24485,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="527" spans="1:14" ht="30" customHeight="1">
+    <row r="527" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="s">
         <v>21</v>
       </c>
@@ -24530,7 +24529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="528" spans="1:14" ht="30" customHeight="1">
+    <row r="528" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="1" t="s">
         <v>21</v>
       </c>
@@ -24574,7 +24573,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="529" spans="1:14" ht="30" customHeight="1">
+    <row r="529" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
         <v>21</v>
       </c>
@@ -24618,7 +24617,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="530" spans="1:14" ht="30" customHeight="1">
+    <row r="530" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
         <v>21</v>
       </c>
@@ -24662,7 +24661,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="531" spans="1:14" ht="30" customHeight="1">
+    <row r="531" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
         <v>21</v>
       </c>
@@ -24706,7 +24705,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="532" spans="1:14" ht="30" customHeight="1">
+    <row r="532" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
         <v>21</v>
       </c>
@@ -24750,7 +24749,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="533" spans="1:14" ht="30" customHeight="1">
+    <row r="533" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
         <v>21</v>
       </c>
@@ -24794,7 +24793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="534" spans="1:14" ht="30" customHeight="1">
+    <row r="534" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
         <v>21</v>
       </c>
@@ -24838,7 +24837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="535" spans="1:14" ht="30" customHeight="1">
+    <row r="535" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
         <v>21</v>
       </c>
@@ -24882,7 +24881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="536" spans="1:14" ht="30" customHeight="1">
+    <row r="536" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
         <v>21</v>
       </c>
@@ -24926,7 +24925,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="537" spans="1:14" ht="30" customHeight="1">
+    <row r="537" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
         <v>21</v>
       </c>
@@ -24970,7 +24969,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="538" spans="1:14" ht="30" customHeight="1">
+    <row r="538" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
         <v>21</v>
       </c>
@@ -25014,7 +25013,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="539" spans="1:14" ht="30" customHeight="1">
+    <row r="539" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
         <v>21</v>
       </c>
@@ -25058,7 +25057,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="540" spans="1:14" ht="30" customHeight="1">
+    <row r="540" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="1" t="s">
         <v>21</v>
       </c>
@@ -25102,7 +25101,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="541" spans="1:14" ht="30" customHeight="1">
+    <row r="541" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="1" t="s">
         <v>21</v>
       </c>
@@ -25146,7 +25145,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="542" spans="1:14" ht="30" customHeight="1">
+    <row r="542" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="1" t="s">
         <v>21</v>
       </c>
@@ -25190,7 +25189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="543" spans="1:14" ht="30" customHeight="1">
+    <row r="543" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="1" t="s">
         <v>21</v>
       </c>
@@ -25234,7 +25233,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="544" spans="1:14" ht="30" customHeight="1">
+    <row r="544" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="1" t="s">
         <v>21</v>
       </c>
@@ -25278,7 +25277,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="545" spans="1:14" ht="30" customHeight="1">
+    <row r="545" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="1" t="s">
         <v>21</v>
       </c>
@@ -25322,7 +25321,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="546" spans="1:14" ht="30" customHeight="1">
+    <row r="546" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="1" t="s">
         <v>21</v>
       </c>
@@ -25366,7 +25365,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="547" spans="1:14" ht="30" customHeight="1">
+    <row r="547" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="1" t="s">
         <v>21</v>
       </c>
@@ -25410,7 +25409,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="548" spans="1:14" ht="30" customHeight="1">
+    <row r="548" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="1" t="s">
         <v>21</v>
       </c>
@@ -25454,7 +25453,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="549" spans="1:14" ht="30" customHeight="1">
+    <row r="549" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="s">
         <v>21</v>
       </c>
@@ -25498,7 +25497,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="550" spans="1:14" ht="30" customHeight="1">
+    <row r="550" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="s">
         <v>21</v>
       </c>
@@ -25542,7 +25541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="551" spans="1:14" ht="30" customHeight="1">
+    <row r="551" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="1" t="s">
         <v>21</v>
       </c>
@@ -25586,7 +25585,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="552" spans="1:14" ht="30" customHeight="1">
+    <row r="552" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="1" t="s">
         <v>21</v>
       </c>
@@ -25630,7 +25629,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="553" spans="1:14" ht="30" customHeight="1">
+    <row r="553" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="1" t="s">
         <v>21</v>
       </c>
@@ -25675,6 +25674,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O553" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
   </dataValidations>
@@ -25746,17 +25746,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" customWidth="1"/>
-    <col min="9" max="9" width="28.54296875" customWidth="1"/>
-    <col min="11" max="11" width="33.1796875" customWidth="1"/>
-    <col min="13" max="13" width="24.26953125" customWidth="1"/>
-    <col min="15" max="15" width="20.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="9" max="9" width="28.5" customWidth="1"/>
+    <col min="11" max="11" width="33.1640625" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>169</v>
       </c>
@@ -25785,7 +25785,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -25814,7 +25814,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -25843,7 +25843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
         <v>32</v>
       </c>
@@ -25866,7 +25866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E5" t="s">
         <v>52</v>
       </c>
@@ -25889,7 +25889,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="I6" t="s">
         <v>9</v>
       </c>
@@ -25903,132 +25903,132 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="O16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="15:15">
+    <row r="17" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="15:15">
+    <row r="18" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="15:15">
+    <row r="19" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O19">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="15:15">
+    <row r="20" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="15:15">
+    <row r="21" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="15:15">
+    <row r="22" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="15:15">
+    <row r="23" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="15:15">
+    <row r="24" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="15:15">
+    <row r="25" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="15:15">
+    <row r="26" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="15:15">
+    <row r="27" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="15:15">
+    <row r="28" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="15:15">
+    <row r="29" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="15:15">
+    <row r="30" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="15:15">
+    <row r="31" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="15:15">
+    <row r="32" spans="15:15" x14ac:dyDescent="0.2">
       <c r="O32">
         <v>30</v>
       </c>
@@ -26041,15 +26041,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" thickBot="1">
+    <row r="1" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>191</v>
       </c>
@@ -26060,7 +26060,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.5">
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -26075,7 +26075,7 @@
       </c>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="1:6" ht="16" thickBot="1">
+    <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -26090,7 +26090,7 @@
       </c>
       <c r="F3" s="17"/>
     </row>
-    <row r="4" spans="1:6" ht="15.5">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -26105,7 +26105,7 @@
       </c>
       <c r="F4" s="17"/>
     </row>
-    <row r="5" spans="1:6" ht="16" thickBot="1">
+    <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -26120,7 +26120,7 @@
       </c>
       <c r="F5" s="17"/>
     </row>
-    <row r="6" spans="1:6" ht="15.5">
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -26135,7 +26135,7 @@
       </c>
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:6" ht="16" thickBot="1">
+    <row r="7" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:6" ht="15.5">
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -26165,7 +26165,7 @@
       </c>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:6" ht="16" thickBot="1">
+    <row r="9" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -26180,7 +26180,7 @@
       </c>
       <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:6" ht="15.5">
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -26195,7 +26195,7 @@
       </c>
       <c r="F10" s="17"/>
     </row>
-    <row r="11" spans="1:6" ht="16" thickBot="1">
+    <row r="11" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>10</v>
       </c>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="F11" s="17"/>
     </row>
-    <row r="12" spans="1:6" ht="15.5">
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -26225,7 +26225,7 @@
       </c>
       <c r="F12" s="17"/>
     </row>
-    <row r="13" spans="1:6" ht="16" thickBot="1">
+    <row r="13" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="F13" s="17"/>
     </row>
-    <row r="14" spans="1:6" ht="15.5">
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -26255,7 +26255,7 @@
       </c>
       <c r="F14" s="17"/>
     </row>
-    <row r="15" spans="1:6" ht="16" thickBot="1">
+    <row r="15" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -26270,7 +26270,7 @@
       </c>
       <c r="F15" s="17"/>
     </row>
-    <row r="16" spans="1:6" ht="15.5">
+    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -26286,7 +26286,7 @@
       <c r="E16" s="19"/>
       <c r="F16" s="17"/>
     </row>
-    <row r="17" spans="1:6" ht="16" thickBot="1">
+    <row r="17" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -26301,7 +26301,7 @@
       </c>
       <c r="F17" s="17"/>
     </row>
-    <row r="18" spans="1:6" ht="15.5">
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -26316,7 +26316,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:6" ht="16" thickBot="1">
+    <row r="19" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>18</v>
       </c>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="F19" s="17"/>
     </row>
-    <row r="20" spans="1:6" ht="15.5">
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -26346,7 +26346,7 @@
       </c>
       <c r="F20" s="17"/>
     </row>
-    <row r="21" spans="1:6" ht="16" thickBot="1">
+    <row r="21" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>20</v>
       </c>
@@ -26361,7 +26361,7 @@
       </c>
       <c r="F21" s="17"/>
     </row>
-    <row r="22" spans="1:6" ht="15.5">
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>21</v>
       </c>
@@ -26376,7 +26376,7 @@
       </c>
       <c r="F22" s="17"/>
     </row>
-    <row r="23" spans="1:6" ht="16" thickBot="1">
+    <row r="23" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>22</v>
       </c>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="1:6" ht="15.5">
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -26406,7 +26406,7 @@
       </c>
       <c r="F24" s="17"/>
     </row>
-    <row r="25" spans="1:6" ht="16" thickBot="1">
+    <row r="25" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>24</v>
       </c>
@@ -26420,7 +26420,7 @@
         <v>2.3148148148148149E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.5">
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -26434,7 +26434,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" thickBot="1">
+    <row r="27" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>26</v>
       </c>
@@ -26448,7 +26448,7 @@
         <v>6.3425925925925924E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.5">
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -26462,7 +26462,7 @@
         <v>9.3287037037037036E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16" thickBot="1">
+    <row r="29" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>28</v>
       </c>
@@ -26476,7 +26476,7 @@
         <v>1.2916666666666667E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.5">
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -26490,7 +26490,7 @@
         <v>5.185185185185185E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="16" thickBot="1">
+    <row r="31" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>30</v>
       </c>
@@ -26512,18 +26512,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="9" max="9" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="9" max="9" width="22.5" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.7265625" customWidth="1"/>
+    <col min="12" max="12" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16" thickBot="1">
+    <row r="1" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>191</v>
       </c>
@@ -26534,7 +26534,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.5">
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -26552,7 +26552,7 @@
       <c r="K2" s="16"/>
       <c r="L2" s="16"/>
     </row>
-    <row r="3" spans="1:12" ht="16" thickBot="1">
+    <row r="3" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -26571,7 +26571,7 @@
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" ht="15.5">
+    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -26590,7 +26590,7 @@
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="16" thickBot="1">
+    <row r="5" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -26609,7 +26609,7 @@
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="15.5">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -26628,7 +26628,7 @@
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="16" thickBot="1">
+    <row r="7" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -26647,7 +26647,7 @@
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="15.5">
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -26666,7 +26666,7 @@
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="16" thickBot="1">
+    <row r="9" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -26685,7 +26685,7 @@
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="15.5">
+    <row r="10" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -26704,7 +26704,7 @@
       <c r="K10" s="17"/>
       <c r="L10" s="16"/>
     </row>
-    <row r="11" spans="1:12" ht="16" thickBot="1">
+    <row r="11" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>10</v>
       </c>
@@ -26723,7 +26723,7 @@
       <c r="K11" s="17"/>
       <c r="L11" s="16"/>
     </row>
-    <row r="12" spans="1:12" ht="15.5">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -26742,7 +26742,7 @@
       <c r="K12" s="17"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" spans="1:12" ht="16" thickBot="1">
+    <row r="13" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -26761,7 +26761,7 @@
       <c r="K13" s="17"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" ht="15.5">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -26780,7 +26780,7 @@
       <c r="K14" s="17"/>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="16" thickBot="1">
+    <row r="15" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -26798,7 +26798,7 @@
       <c r="K15" s="17"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="15.5">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -26816,7 +26816,7 @@
       <c r="K16" s="17"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="16" thickBot="1">
+    <row r="17" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -26834,7 +26834,7 @@
       <c r="K17" s="17"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="1:12" ht="15.5">
+    <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -26852,7 +26852,7 @@
       <c r="K18" s="17"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" ht="16" thickBot="1">
+    <row r="19" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>18</v>
       </c>
@@ -26870,7 +26870,7 @@
       <c r="K19" s="17"/>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="15.5">
+    <row r="20" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -26888,7 +26888,7 @@
       <c r="K20" s="17"/>
       <c r="L20" s="16"/>
     </row>
-    <row r="21" spans="1:12" ht="16" thickBot="1">
+    <row r="21" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>20</v>
       </c>
@@ -26906,7 +26906,7 @@
       <c r="K21" s="17"/>
       <c r="L21" s="16"/>
     </row>
-    <row r="22" spans="1:12" ht="15.5">
+    <row r="22" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>21</v>
       </c>
@@ -26924,7 +26924,7 @@
       <c r="K22" s="17"/>
       <c r="L22" s="16"/>
     </row>
-    <row r="23" spans="1:12" ht="16" thickBot="1">
+    <row r="23" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>22</v>
       </c>
@@ -26942,7 +26942,7 @@
       <c r="K23" s="17"/>
       <c r="L23" s="16"/>
     </row>
-    <row r="24" spans="1:12" ht="15.5">
+    <row r="24" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -26960,7 +26960,7 @@
       <c r="K24" s="17"/>
       <c r="L24" s="16"/>
     </row>
-    <row r="25" spans="1:12" ht="16" thickBot="1">
+    <row r="25" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>24</v>
       </c>
@@ -26978,7 +26978,7 @@
       <c r="K25" s="17"/>
       <c r="L25" s="16"/>
     </row>
-    <row r="26" spans="1:12" ht="15.5">
+    <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -26996,7 +26996,7 @@
       <c r="K26" s="17"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27" spans="1:12" ht="16" thickBot="1">
+    <row r="27" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>26</v>
       </c>
@@ -27014,7 +27014,7 @@
       <c r="K27" s="17"/>
       <c r="L27" s="16"/>
     </row>
-    <row r="28" spans="1:12" ht="15.5">
+    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -27032,7 +27032,7 @@
       <c r="K28" s="17"/>
       <c r="L28" s="16"/>
     </row>
-    <row r="29" spans="1:12" ht="16" thickBot="1">
+    <row r="29" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>28</v>
       </c>
@@ -27050,7 +27050,7 @@
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
     </row>
-    <row r="30" spans="1:12" ht="15.5">
+    <row r="30" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -27068,7 +27068,7 @@
       <c r="K30" s="17"/>
       <c r="L30" s="16"/>
     </row>
-    <row r="31" spans="1:12" ht="16" thickBot="1">
+    <row r="31" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>30</v>
       </c>
@@ -27094,15 +27094,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC903D6C-3B1E-4A55-9A38-8B7FEC304466}">
   <dimension ref="A1:E61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="21.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" thickBot="1">
+    <row r="1" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -27115,11 +27115,11 @@
       <c r="D1" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="16" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16" thickBot="1">
+    <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -27153,7 +27153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5">
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -27170,7 +27170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" thickBot="1">
+    <row r="5" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -27187,7 +27187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16" thickBot="1">
+    <row r="7" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -27221,7 +27221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.5">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -27238,7 +27238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16" thickBot="1">
+    <row r="9" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -27255,7 +27255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.5">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -27272,7 +27272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16" thickBot="1">
+    <row r="11" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>10</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.5">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -27306,7 +27306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16" thickBot="1">
+    <row r="13" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -27323,7 +27323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.5">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -27340,7 +27340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16" thickBot="1">
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -27357,7 +27357,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.5">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -27374,7 +27374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16" thickBot="1">
+    <row r="17" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -27391,7 +27391,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.5">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -27408,7 +27408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16" thickBot="1">
+    <row r="19" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>18</v>
       </c>
@@ -27425,7 +27425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.5">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -27442,7 +27442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16" thickBot="1">
+    <row r="21" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>20</v>
       </c>
@@ -27459,7 +27459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.5">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>21</v>
       </c>
@@ -27476,7 +27476,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16" thickBot="1">
+    <row r="23" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>22</v>
       </c>
@@ -27493,7 +27493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.5">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -27510,7 +27510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16" thickBot="1">
+    <row r="25" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>24</v>
       </c>
@@ -27527,7 +27527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.5">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -27544,7 +27544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16" thickBot="1">
+    <row r="27" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>26</v>
       </c>
@@ -27561,7 +27561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.5">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -27578,7 +27578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16" thickBot="1">
+    <row r="29" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>28</v>
       </c>
@@ -27595,7 +27595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.5">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -27612,7 +27612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16" thickBot="1">
+    <row r="31" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>30</v>
       </c>
@@ -27629,7 +27629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.5">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>1</v>
       </c>
@@ -27646,7 +27646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16" thickBot="1">
+    <row r="33" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>2</v>
       </c>
@@ -27663,7 +27663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.5">
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>3</v>
       </c>
@@ -27680,7 +27680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16" thickBot="1">
+    <row r="35" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>4</v>
       </c>
@@ -27697,7 +27697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.5">
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>5</v>
       </c>
@@ -27714,7 +27714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16" thickBot="1">
+    <row r="37" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>6</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.5">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>7</v>
       </c>
@@ -27748,7 +27748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16" thickBot="1">
+    <row r="39" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>8</v>
       </c>
@@ -27765,7 +27765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.5">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>9</v>
       </c>
@@ -27782,7 +27782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16" thickBot="1">
+    <row r="41" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>10</v>
       </c>
@@ -27799,7 +27799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.5">
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>11</v>
       </c>
@@ -27816,7 +27816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16" thickBot="1">
+    <row r="43" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>12</v>
       </c>
@@ -27833,7 +27833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.5">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>13</v>
       </c>
@@ -27850,7 +27850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16" thickBot="1">
+    <row r="45" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <v>14</v>
       </c>
@@ -27867,7 +27867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.5">
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>15</v>
       </c>
@@ -27884,7 +27884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16" thickBot="1">
+    <row r="47" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>16</v>
       </c>
@@ -27901,7 +27901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.5">
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>17</v>
       </c>
@@ -27918,7 +27918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16" thickBot="1">
+    <row r="49" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>18</v>
       </c>
@@ -27935,7 +27935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.5">
+    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>19</v>
       </c>
@@ -27952,7 +27952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16" thickBot="1">
+    <row r="51" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>20</v>
       </c>
@@ -27969,7 +27969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.5">
+    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>21</v>
       </c>
@@ -27986,7 +27986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16" thickBot="1">
+    <row r="53" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <v>22</v>
       </c>
@@ -28003,7 +28003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.5">
+    <row r="54" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
         <v>23</v>
       </c>
@@ -28020,7 +28020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16" thickBot="1">
+    <row r="55" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <v>24</v>
       </c>
@@ -28037,7 +28037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.5">
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
         <v>25</v>
       </c>
@@ -28054,7 +28054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16" thickBot="1">
+    <row r="57" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <v>26</v>
       </c>
@@ -28071,7 +28071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.5">
+    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="10">
         <v>27</v>
       </c>
@@ -28088,7 +28088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="16" thickBot="1">
+    <row r="59" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <v>28</v>
       </c>
@@ -28105,7 +28105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.5">
+    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="10">
         <v>29</v>
       </c>
@@ -28122,7 +28122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="16" thickBot="1">
+    <row r="61" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <v>30</v>
       </c>
